--- a/outputs/EVINV-POC-001/phase1/phase1-resource-milestone-schedule.xlsx
+++ b/outputs/EVINV-POC-001/phase1/phase1-resource-milestone-schedule.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 1 | Gate: 1 | Generated: 2026-08-18T03:49:20.825Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 1 | Gate: 1 | Generated: 2026-08-18T12:53:10.149Z</v>
       </c>
     </row>
     <row r="4">
@@ -434,37 +434,37 @@
     </row>
     <row r="5">
       <c r="B5" t="str">
-        <v>MS1 — Program Kickoff</v>
+        <v>Project Kickoff</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="str">
-        <v>MS2 — Architecture &amp; Topology Review</v>
+        <v>Requirements Freeze &amp; Architecture Review</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="str">
-        <v>MS3 — Preliminary BOM &amp; Supplier Selection</v>
+        <v>Preliminary Design Review (PDR)</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="str">
-        <v>MS4 — Detailed Design Release</v>
+        <v>Critical Design Review (CDR) &amp; Prototype Build Authorization</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="str">
-        <v>MS5 — Prototype Build &amp; Bring-Up</v>
+        <v>Prototype Build &amp; Bring-Up</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="str">
-        <v>MS6 — Validation Testing (150 kW / 220 kW)</v>
+        <v>Validation Testing &amp; Pre-Compliance</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="str">
-        <v>MS7 — Production Readiness Review (PRR)</v>
+        <v>Production Readiness Review (PRR) &amp; Gate G3</v>
       </c>
     </row>
   </sheetData>
